--- a/docs/College-List-Template.xlsx
+++ b/docs/College-List-Template.xlsx
@@ -12,11 +12,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="85">
   <si>
     <t>College Name</t>
   </si>
   <si>
+    <t>College Code</t>
+  </si>
+  <si>
     <t>Location</t>
   </si>
   <si>
@@ -26,6 +29,9 @@
     <t>RV College of Engineering</t>
   </si>
   <si>
+    <t>1RV</t>
+  </si>
+  <si>
     <t>Bengaluru</t>
   </si>
   <si>
@@ -35,84 +41,126 @@
     <t>BMS College of Engineering</t>
   </si>
   <si>
+    <t>1BM</t>
+  </si>
+  <si>
     <t>Bull Temple Road, Basavanagudi, Bengaluru 560019</t>
   </si>
   <si>
     <t>PES University</t>
   </si>
   <si>
+    <t>1PE</t>
+  </si>
+  <si>
     <t>100 Feet Ring Road, BSK III Stage, Bengaluru 560085</t>
   </si>
   <si>
     <t>MS Ramaiah Institute of Technology</t>
   </si>
   <si>
+    <t>1MS</t>
+  </si>
+  <si>
     <t>MSR Nagar, MSRIT Post, Bengaluru 560054</t>
   </si>
   <si>
     <t>Bangalore Institute of Technology</t>
   </si>
   <si>
+    <t>1BI</t>
+  </si>
+  <si>
     <t>KR Road, VV Puram, Bengaluru 560004</t>
   </si>
   <si>
     <t>Dayananda Sagar College of Engineering</t>
   </si>
   <si>
+    <t>1DS</t>
+  </si>
+  <si>
     <t>Shavige Malleshwara Hills, Kumaraswamy Layout, Bengaluru 560078</t>
   </si>
   <si>
     <t>New Horizon College of Engineering</t>
   </si>
   <si>
+    <t>1NH</t>
+  </si>
+  <si>
     <t>Ring Road, Bellandur Post, Bengaluru 560103</t>
   </si>
   <si>
     <t>Acharya Institute of Technology</t>
   </si>
   <si>
+    <t>1AY</t>
+  </si>
+  <si>
     <t>Soldevanahalli, Hesaraghatta Road, Bengaluru 560107</t>
   </si>
   <si>
     <t>Sir M Visvesvaraya Institute of Technology</t>
   </si>
   <si>
+    <t>1MV</t>
+  </si>
+  <si>
     <t>Hunasamaranahalli, Yelahanka, Bengaluru 562157</t>
   </si>
   <si>
     <t>T John Institute of Technology</t>
   </si>
   <si>
+    <t>1TJ</t>
+  </si>
+  <si>
     <t>Gottigere, Bannerghatta Road, Bengaluru 560083</t>
   </si>
   <si>
     <t>Nitte Meenakshi Institute of Technology</t>
   </si>
   <si>
+    <t>1NT</t>
+  </si>
+  <si>
     <t>Govindapura, Yelahanka, Bengaluru 560064</t>
   </si>
   <si>
     <t>Sambhram Institute of Technology</t>
   </si>
   <si>
+    <t>1SB</t>
+  </si>
+  <si>
     <t>MS Palya, Jalahalli East, Bengaluru 560097</t>
   </si>
   <si>
     <t>CMR Institute of Technology</t>
   </si>
   <si>
+    <t>1CR</t>
+  </si>
+  <si>
     <t>AECS Layout, ITPL Main Road, Bengaluru 560037</t>
   </si>
   <si>
     <t>Global Academy of Technology</t>
   </si>
   <si>
+    <t>1GA</t>
+  </si>
+  <si>
     <t>Rajarajeshwari Nagar, Bengaluru 560098</t>
   </si>
   <si>
     <t>Siddaganga Institute of Technology</t>
   </si>
   <si>
+    <t>1SI</t>
+  </si>
+  <si>
     <t>Tumakuru</t>
   </si>
   <si>
@@ -122,6 +170,9 @@
     <t>PES Institute of Technology and Management</t>
   </si>
   <si>
+    <t>4PS</t>
+  </si>
+  <si>
     <t>Shivamogga</t>
   </si>
   <si>
@@ -131,6 +182,9 @@
     <t>Malnad College of Engineering</t>
   </si>
   <si>
+    <t>4MC</t>
+  </si>
+  <si>
     <t>Hassan</t>
   </si>
   <si>
@@ -140,6 +194,9 @@
     <t>JSS Science and Technology University</t>
   </si>
   <si>
+    <t>4JS</t>
+  </si>
+  <si>
     <t>Mysuru</t>
   </si>
   <si>
@@ -149,12 +206,18 @@
     <t>NIE Institute of Technology</t>
   </si>
   <si>
+    <t>4NI</t>
+  </si>
+  <si>
     <t>Koorgalli, Hootagalli, Mysuru 570018</t>
   </si>
   <si>
     <t>Channabasaveshwara Institute of Technology</t>
   </si>
   <si>
+    <t>1CT</t>
+  </si>
+  <si>
     <t>NH 206, Gubbi, Tumakuru 572216</t>
   </si>
   <si>
@@ -176,16 +239,16 @@
     <t>Filling in your own list</t>
   </si>
   <si>
-    <t>•  Keep the three column headings on row 1 exactly as they are: College Name, Location, Address.</t>
-  </si>
-  <si>
-    <t>•  Only College Name is required. Location and Address may be left blank.</t>
+    <t>•  Keep the column headings on row 1: College Name, College Code, Location, Address.</t>
+  </si>
+  <si>
+    <t>•  Only College Name is required. Code, Location and Address may be left blank.</t>
   </si>
   <si>
     <t>•  One college per row. Do not merge cells or leave blank rows in the middle.</t>
   </si>
   <si>
-    <t>•  Names are saved in CAPITALS automatically — type them however you like.</t>
+    <t>•  Names and codes are saved in CAPITALS automatically — type them however you like.</t>
   </si>
   <si>
     <t>•  The list is sorted alphabetically by the portal, so the order here does not matter.</t>
@@ -200,10 +263,10 @@
     <t>•  The importer reads the headings, so the columns can be in any order.</t>
   </si>
   <si>
-    <t>•  If row 1 has no recognisable headings, the first three columns are read as</t>
-  </si>
-  <si>
-    <t>•  College Name, Location and Address in that order.</t>
+    <t>•  If row 1 has no recognisable headings, the first four columns are read as</t>
+  </si>
+  <si>
+    <t>•  College Name, College Code, Location and Address in that order.</t>
   </si>
 </sst>
 </file>
@@ -643,15 +706,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="62" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,229 +725,292 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" ht="19" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C21"/>
+  <autoFilter ref="A1:D21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -900,162 +1027,162 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
